--- a/Data/EC/NIT-9008130312.xlsx
+++ b/Data/EC/NIT-9008130312.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura Wilches\Documents\2_ Macro Comfenalco Cartagena\Macro Aviso Incumplimiento y demás\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Operaciones\OneDrive - NIYARAKY COLOMBIA SAS OLD2\Escritorio\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A6FBA3E-A8CA-4D0A-9255-D6604BEE61E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9C7DC6C-3516-4C9C-A749-02DFBE8A4541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{039C4A25-D8C2-439E-AD51-B40B82361311}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{1BE714C8-A7A8-4B6C-8047-2B05388540F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -680,22 +680,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>633769</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>55950</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>437794</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>125025</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6891BBA4-F32E-A0A2-DECA-0D5B82EACE98}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2BA02F7-3DFD-FF6D-4726-5F107BCDCC2D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -704,7 +704,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -717,7 +717,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="890944" y="236925"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1046,23 +1046,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCE7CB45-BEAB-425C-9AE3-CCFAFB989A1F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1247651-A57D-4F08-BCEF-402274FF51E2}">
   <dimension ref="B2:J94"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
@@ -1075,7 +1075,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1086,7 +1086,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1097,7 +1097,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1108,8 +1108,8 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>82</v>
       </c>
@@ -1124,8 +1124,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1140,8 +1140,8 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>83</v>
       </c>
@@ -1156,8 +1156,8 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>84</v>
       </c>
@@ -1176,7 +1176,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1205,7 +1205,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1228,7 +1228,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1251,7 +1251,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1274,7 +1274,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1297,7 +1297,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1320,7 +1320,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1343,7 +1343,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1366,7 +1366,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1389,7 +1389,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1412,7 +1412,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1435,7 +1435,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1458,7 +1458,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1481,7 +1481,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1504,7 +1504,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1527,7 +1527,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1550,7 +1550,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1573,7 +1573,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1596,7 +1596,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1619,7 +1619,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1642,7 +1642,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1665,7 +1665,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1688,7 +1688,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1711,7 +1711,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1734,7 +1734,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1757,7 +1757,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1780,7 +1780,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1803,7 +1803,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1826,7 +1826,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1849,7 +1849,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1872,7 +1872,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1895,7 +1895,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1918,7 +1918,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -1941,7 +1941,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -1964,7 +1964,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -1987,7 +1987,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -2010,7 +2010,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -2033,7 +2033,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -2056,7 +2056,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2079,7 +2079,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2102,7 +2102,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2125,7 +2125,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2148,7 +2148,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2171,7 +2171,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2194,7 +2194,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2217,7 +2217,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2240,7 +2240,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2263,7 +2263,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2286,7 +2286,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2309,7 +2309,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2332,7 +2332,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2355,7 +2355,7 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
@@ -2378,7 +2378,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2401,7 +2401,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
@@ -2424,7 +2424,7 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
@@ -2447,7 +2447,7 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
@@ -2470,7 +2470,7 @@
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
@@ -2493,7 +2493,7 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
@@ -2516,7 +2516,7 @@
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
@@ -2539,7 +2539,7 @@
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
@@ -2562,7 +2562,7 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>8</v>
       </c>
@@ -2585,7 +2585,7 @@
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>8</v>
       </c>
@@ -2608,7 +2608,7 @@
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>8</v>
       </c>
@@ -2631,7 +2631,7 @@
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
         <v>8</v>
       </c>
@@ -2654,7 +2654,7 @@
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
         <v>8</v>
       </c>
@@ -2677,7 +2677,7 @@
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
         <v>8</v>
       </c>
@@ -2700,7 +2700,7 @@
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
         <v>8</v>
       </c>
@@ -2723,7 +2723,7 @@
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
         <v>8</v>
       </c>
@@ -2746,7 +2746,7 @@
       <c r="I82" s="19"/>
       <c r="J82" s="20"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
         <v>8</v>
       </c>
@@ -2769,7 +2769,7 @@
       <c r="I83" s="19"/>
       <c r="J83" s="20"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
         <v>8</v>
       </c>
@@ -2792,7 +2792,7 @@
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
         <v>8</v>
       </c>
@@ -2815,7 +2815,7 @@
       <c r="I85" s="19"/>
       <c r="J85" s="20"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
         <v>8</v>
       </c>
@@ -2838,7 +2838,7 @@
       <c r="I86" s="19"/>
       <c r="J86" s="20"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
         <v>8</v>
       </c>
@@ -2861,7 +2861,7 @@
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="21" t="s">
         <v>8</v>
       </c>
@@ -2884,7 +2884,7 @@
       <c r="I88" s="25"/>
       <c r="J88" s="26"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="32" t="s">
         <v>90</v>
       </c>
@@ -2895,7 +2895,7 @@
       <c r="I93" s="1"/>
       <c r="J93" s="1"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="32" t="s">
         <v>89</v>
       </c>
